--- a/docs/Cronograma_TG_DLHM.xlsx
+++ b/docs/Cronograma_TG_DLHM.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Hitos" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tareas'!$A$3:$I$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tareas'!$A$3:$I$81</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
@@ -1314,7 +1314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="7" customWidth="1" style="22" min="1" max="1"/>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>En curso</t>
         </is>
       </c>
       <c r="H20" s="12" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
-          <t>VENCIDA el 28/08 y abierta al 31/08. Es la dependencia mas critica del cronograma: la Fase 2 arranca el 14/09 -dos semanas, con el receso de por medio- y sin lambda, pitch, sensor, L, z y NA reales el barrido de la tarea 30 se corre sobre valores inventados y hay que repetirlo. El acceso al montaje ya no es el bloqueo: la sesion de familiarizacion (tarea 16) y la reserva de laboratorio (tarea 18) estan hechas. AL 01/09 ES EL FOCO DE LA SEMANA 8: quedan cuatro dias habiles (1-4 sep) antes del receso, y despues del receso solo queda la semana del 14/09, que es cuando arranca la Fase 2 que depende de estos numeros. Al 01/09 su entregable esta PREPARADO Y VACIO (tarea 73): docs/hoja_parametros_montaje.md es el checklist que se lleva al laboratorio y CamposT/montaje.py el destino de los numeros. Faltan los 15 valores; cualquier cuenta que use uno de ellos falla en el acto en vez de propagar un valor inventado. CONFIRMADO el 01/09 que hay acceso al montaje esta misma semana, asi que la tarea deja de depender de la reserva de las semanas 9 a 11.</t>
+          <t>VENCIDA el 28/08 y abierta al 31/08. Es la dependencia mas critica del cronograma: la Fase 2 arranca el 14/09 -dos semanas, con el receso de por medio- y sin lambda, pitch, sensor, L, z y NA reales el barrido de la tarea 30 se corre sobre valores inventados y hay que repetirlo. El acceso al montaje ya no es el bloqueo: la sesion de familiarizacion (tarea 16) y la reserva de laboratorio (tarea 18) estan hechas. AL 01/09 ES EL FOCO DE LA SEMANA 8: quedan cuatro dias habiles (1-4 sep) antes del receso, y despues del receso solo queda la semana del 14/09, que es cuando arranca la Fase 2 que depende de estos numeros. Al 01/09 su entregable esta PREPARADO Y VACIO (tarea 73): docs/hoja_parametros_montaje.md es el checklist que se lleva al laboratorio y CamposT/montaje.py el destino de los numeros. Faltan los 15 valores; cualquier cuenta que use uno de ellos falla en el acto en vez de propagar un valor inventado. CONFIRMADO el 01/09 que hay acceso al montaje esta misma semana, asi que la tarea deja de depender de la reserva de las semanas 9 a 11. EN CURSO desde el 20/09 (commit 4e0927c0e): montaje.py tiene ya lambda, pinhole, los dos pasos de pixel y L medidos, 5 de los 15 parametros. Quedan 10 pendientes.</t>
         </is>
       </c>
     </row>
@@ -2389,17 +2389,17 @@
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="I27" s="13" t="inlineStr">
         <is>
-          <t>Adelantada. figura_escenario.py (commit c6963d1) fija la primitiva: la lente f = -300 mm de la Tabla 1, aplicada sobre la cintura, deja el haz con R = 300 mm y la cintura intacta, o sea un pinhole virtual. Se modela el frente esferico divergente, no la lente. Falta pasar de la figura al desarrollo escrito.</t>
+          <t>Adelantada. figura_escenario.py (commit c6963d1) fija la primitiva: la lente f = -300 mm de la Tabla 1, aplicada sobre la cintura, deja el haz con R = 300 mm y la cintura intacta, o sea un pinhole virtual. Se modela el frente esferico divergente, no la lente. Falta pasar de la figura al desarrollo escrito. Reunion con el asesor el 08/09 (docs/reunion_asesor.pdf): la fecha limite se corrio al 25/09 (fin de semana 10). CERRADA el 22/09: docs/tarea24_mpasm_onda_esferica.pdf es el desarrollo escrito que faltaba, sobre la onda esferica en MPASM.</t>
         </is>
       </c>
     </row>
@@ -4316,7 +4316,7 @@
         </is>
       </c>
     </row>
-    <row r="75">
+    <row r="75" s="22">
       <c r="A75" s="12" t="n">
         <v>72</v>
       </c>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
     </row>
-    <row r="76">
+    <row r="76" s="22">
       <c r="A76" s="12" t="n">
         <v>73</v>
       </c>
@@ -4402,7 +4402,7 @@
         </is>
       </c>
     </row>
-    <row r="77">
+    <row r="77" s="22">
       <c r="A77" s="12" t="n">
         <v>74</v>
       </c>
@@ -4447,8 +4447,180 @@
         </is>
       </c>
     </row>
+    <row r="78" ht="25.5" customHeight="1" s="22">
+      <c r="A78" s="12" t="n">
+        <v>75</v>
+      </c>
+      <c r="B78" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="C78" s="12" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D78" s="13" t="inlineStr">
+        <is>
+          <t>Corregir el bug de ejes cruzados en mi_prueba_mpasm y anadir guarda de convencion de ejes</t>
+        </is>
+      </c>
+      <c r="E78" s="13" t="inlineStr">
+        <is>
+          <t>Guarda de ejes en los sidecar + mpasm_minimo.py + montaje con datos medidos</t>
+        </is>
+      </c>
+      <c r="F78" s="12" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="G78" s="12" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="H78" s="12" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="I78" s="13" t="inlineStr">
+        <is>
+          <t>Commit 4e0927c0e. _comprobar_con_el_sidecar() de mi_prueba_angular, _blas y _mpasm compara ahora tambien la CONVENCION DE EJES contra el .txt del holograma, no solo lambda y delta: angularSpectrum de pyDHM cruza dfx y dfy (cada eje con la longitud del OTRO), espectro_angular_bl y mpasm_bloques llevan cada uno el suyo; en malla cuadrada da igual, en rectangular son dos transformadas distintas y la vuelta no deshace la ida, sin lanzar ni avisar. mi_prueba_mpasm era la victima: EJES_CRUZADOS = True describia al holograma de su RUTA y no a mpasm_bloques, y silenciaba la guarda. MEDIDO sobre la misma configuracion (mismo holograma, mismo propagador, misma metrica, cruzando solo las frecuencias): con cada eje su longitud, foco 16.500 mm, corr 0.8089, altura 0.0161; con los ejes cruzados (los del .txt), foco 10.000 mm, corr 0.8615, altura 0.0792, para un holograma hecho a 10.000 mm. Ahora EJES_CRUZADOS = False y RUTA apunta a blas/z0200.000.npy (BL-ASM, ejes en su sitio): enfoca en 200.000 mm con corr 0.9132, igual al docstring. Sobre el .png de al lado (sin fase) la curva no tiene pico (0.6717 a 0.6744 entre 199.80 y 200.20, subiendo al final): la gemela pesa tanto como la imagen real. retro_mpasm: Kf POR EJE en vez del min() de los dos, porque Kf va como 1/sqrt(N) y el eje corto pide mas compresion que el largo. Contrastado ademas que mpasm_minimo.mpasm (nuevo, el propagador de Zhao solo) y mpasm_bloques son el mismo algoritmo: 1.7e-15 de diferencia maxima, correlacion 1.000000000000 en CPU/complex128. montaje.py: lambda, pinhole y los dos pasos de pixel y L pasan de SinMedir a valores medidos (insumo de la tarea 17). Nuevos scripts/barrido_foco.py (autofoco con Tamura, Pearson y SSIM) y scripts/propagar_imagen.py, y tests/test_sidecar_ejes.py + tests/test_kf_por_eje_scripts.py. 465 passed, 4 skipped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="25.5" customHeight="1" s="22">
+      <c r="A79" s="12" t="n">
+        <v>76</v>
+      </c>
+      <c r="B79" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="C79" s="12" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D79" s="13" t="inlineStr">
+        <is>
+          <t>Encadenar el SSIM de CPU con la propagacion GPU en barrido_foco</t>
+        </is>
+      </c>
+      <c r="E79" s="13" t="inlineStr">
+        <is>
+          <t>Barrido de foco mas rapido sin perder precision</t>
+        </is>
+      </c>
+      <c r="F79" s="12" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="G79" s="12" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="H79" s="12" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="I79" s="13" t="inlineStr">
+        <is>
+          <t>Commit e1580599b0. SSIM es la unica de las tres metricas de barrido_foco.py que corre en CPU (skimage no tiene version GPU) y mientras se calcula la tarjeta esta parada. El bucle ahora LANZA la propagacion del paso i (mpasm() vuelve enseguida, CuPy encola asincrono) y, mientras la GPU la hace, la CPU cierra el SSIM del paso i-1: el costo por z pasa de la SUMA de los dos lados al MAYOR. No hacen falta hilos, el solapamiento lo da el driver (basta con no sincronizar entre el lanzamiento y el trabajo de CPU); desaparece el cp.cuda.Stream.null.synchronize() explicito. MEDIDO sobre 62 retropropagaciones, BORDE_PX = 1000, Z_REAL = 60, RTX 3050 Laptop, serie vs solapado: con S=1, 42.2 s -&gt; 27.9 s (34% de ahorro, 391-&gt;157 ms/z en la GPU); con S=2, 112.8 s -&gt; 102.0 s (10%, 1503-&gt;1333 ms/z). No llega al techo: SSIM cuesta ~17 s en las cuatro corridas y con S=1 se esconden 14.3 de esos 17 (86%), con S=2 solo 10.8 (63%) aun sobrando sitio para esconderlo entero; queda como hipotesis SIN MEDIR que la copia a CPU y el reparto del pool de CuPy comparten stream con la propagacion. Las curvas salen IDENTICAS bit a bit contra la version en serie en los dos valores de S (comprobado clave por clave del .npz), porque esto mueve el reloj y no los numeros; se escriben por INDICE y no con append, porque el paso i-1 se cierra una vuelta mas tarde que el i. Dos constantes nuevas: EN_CPU (que metricas viven en CPU) y SOLAPAR (apaga el encadenado para remedir en serie), con SOLAPANDO desactivandolo solo cuando no hay GPU que adelantar o no hay metrica de CPU que esconder. Probada tambien la ruta sin tarjeta (GPU=False, malla 512x512): cae a serie y las tres metricas aciertan el foco. 465 passed, 4 skipped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="25.5" customHeight="1" s="22">
+      <c r="A80" s="12" t="n">
+        <v>77</v>
+      </c>
+      <c r="B80" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C80" s="12" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D80" s="13" t="inlineStr">
+        <is>
+          <t>Anadir ROI arrastrable y bloques de memoria a barrido_foco / mpasm_minimo</t>
+        </is>
+      </c>
+      <c r="E80" s="13" t="inlineStr">
+        <is>
+          <t>Barrido de foco enfocable a una region, sin desbordar memoria</t>
+        </is>
+      </c>
+      <c r="F80" s="12" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="G80" s="12" t="inlineStr">
+        <is>
+          <t>En curso</t>
+        </is>
+      </c>
+      <c r="H80" s="12" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="I80" s="13" t="inlineStr">
+        <is>
+          <t>SIN COMMITEAR al 22/09 (arbol de trabajo). ROI en barrido_foco.py: mpasm(ventana=...) evalua la salida solo en una region del plano en vez de recortar el holograma de entrada, para no perder los angulos altos del cono ni meter anillos de corte en la metrica; ROI = None (borde de siempre), True (se arrastra con el raton sobre |U0|^2) o una tupla (X0,Y0,ANCHO,ALTO). Avisa hasta que z el margen sigue tapando los anillos del borde (z_cubre). mpasm_minimo.mpasm gana el parametro ventana (calcula solo esa porcion de la malla de salida; la entrada sigue siendo el holograma entero y Kf no cambia) y arma la funcion de transferencia POR BLOQUES de filas en vez de entera: con 3000x4000 y s=3 los temporales enteros pasaban de 4 GB encima de F, y en Windows el driver no fallaba, desbordaba a RAM y cada z se arrastraba; el paso de bloque es ~64 MB de float64. La mascara arg&gt;0 se aplica por producto y no con indexado booleano, porque el indexado obliga a CuPy a sincronizar y rompia el encadenado SOLAPAR de la tarea 76. fasor() ahora escribe cos/sin directo en el dtype de trabajo en vez de pasar por complex128 (el doble de memoria). De paso, en los parametros del script S baja de 2 a 1 y SOLAPAR de True a False, para volver a medir en serie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="25.5" customHeight="1" s="22">
+      <c r="A81" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="B81" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C81" s="12" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="D81" s="13" t="inlineStr">
+        <is>
+          <t>Implementar el MPASM con la onda esferica exacta para DLHM (CamposT/dlhm.py)</t>
+        </is>
+      </c>
+      <c r="E81" s="13" t="inlineStr">
+        <is>
+          <t>CamposT/dlhm.py + tests/test_dlhm.py + scripts/verif_dlhm_esferico.py</t>
+        </is>
+      </c>
+      <c r="F81" s="12" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="G81" s="12" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="H81" s="12" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="I81" s="13" t="inlineStr">
+        <is>
+          <t>Commit 17b6e2f510. MPASM con la onda esferica EXACTA en los dos sentidos, sin aproximacion paraxial: CamposT/dlhm.py, con holograma() para simular y Reconstructor/reconstruir() para reconstruir; el Reconstructor calcula el espectro del sensor una sola vez para todo un barrido de z. La parte parabolica de e^{ikr}/r va DENTRO de las matrices de la DFT con integrales de Fresnel (ventana_chirp: la DFT exacta de una entrada de banda limitada por un chirp sin muestrear) y el residuo no paraxial punto a punto; la rejilla de frecuencias sale de la geometria, con banda mas ancha que 1/delta (Kf &lt; 1: expansion, no compresion), y se reconstruye c - 1 (con c, la referencia truncada en el borde del sensor bajaba la corr de 0.90 a 0.27). SUPERA LA RECOMENDACION (i) DE LA TAREA 24: el escalado z_eq en la malla delta/M solo se habia validado con objetos lisos de 6 a 30 um; con detalle de ~1.25 um su ida contra Rayleigh-Sommerfeld directo da error 0.47 en el eje, 0.65 a 5.7 grados y 0.89 a 12.4, y la exacta 3.6e-6 en los tres. Sensor entero (N = 3000, borde a 15.3 grados): corr con el objeto 0.969 en la ventana entera (1.0000 hasta 3 grados, 0.925 en la esquina) contra 0.683 del escalado; la misma rejilla sin las ventanas de Fresnel da 0.516, y en N = 2048 entre 0.42 y 0.946 segun el periodo P: acierta por geometria, no por construccion. Coste por z igual al escalado: 0.36 frente a 0.33 s en N = 3000; con 3000x4000 px son 5200x7712 frecuencias (306 MB en complex64), 9.8 s una vez y 0.56 s por z en la RTX 3050. Autofoco por nitidez sobre un holograma de INTENSIDAD del BenchmarkTarget a z = 3 mm: la exacta encuentra 3.0005 mm y el escalado se va al extremo del barrido. Contrastada con reconstruir() de mi_prueba_dlhm (la cadena de Carlos): corr 0.993 con malla PAR y remuestreo de banda limitada; con la malla impar que da malla_remuestreada (2027) solo 0.875, porque su linspace no pasa por f = 0 y desplaza ~1 um. tests/test_dlhm.py: 21 pruebas, 10 de 10 mutaciones detectadas; scripts/verif_dlhm_esferico.py reproduce las cifras; scipy pasa a dependencia. 486 passed, 4 skipped. Rama claude/dlhm-mpasm-esferico, sin fusionar al 27/09. DEUDAS ABIERTAS: la malla impar de malla_remuestreada sigue sin corregir; la imagen gemela no se suprime; no se modela la integracion del pixel; la ida del sensor entero tarda 34 s en GPU; falta decidir si esto cierra las tareas 25 y 27; y hay que revisar la diapositiva 9 (Kf) y el PDF de la tarea 24.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:I77"/>
+  <autoFilter ref="A3:I81"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>

--- a/docs/Cronograma_TG_DLHM.xlsx
+++ b/docs/Cronograma_TG_DLHM.xlsx
@@ -2432,7 +2432,7 @@
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="H28" s="12" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="I28" s="13" t="inlineStr">
         <is>
-          <t>La magnificacion geometrica ya existe: parametro mag de mpasm (r1, r2 de las Ecs. (7)-(8)), verificado en figura_escenario.py con malla de salida 6x. Falta la compensacion de fase de la iluminacion divergente.</t>
+          <t>La magnificacion geometrica ya existe: parametro mag de mpasm (r1, r2 de las Ecs. (7)-(8)), verificado en figura_escenario.py con malla de salida 6x. Falta la compensacion de fase de la iluminacion divergente. CERRADA el 27/09 con la tarea 78 (commit 17b6e2f510), fuera de su fecha del 18/09. La compensacion de fase de la iluminacion divergente es la esferica EXACTA e^{ikr}/r, en los dos sentidos y sin aproximacion paraxial: al reconstruir se multiplica por la de la fuente vista en el sensor (R = L) y se divide por la vista en la muestra (R = z); su parte parabolica va dentro de las matrices de la DFT del MPASM y el residuo punto a punto. La magnificacion geometrica M = L/z es exacta (proyeccion central entre planos paralelos) y entra como la malla de la muestra, delta*z/L, sin reescalar nada. Verificado contra Rayleigh-Sommerfeld directo: 3.6e-6 de error relativo hasta 12.4 grados.</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="H30" s="12" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="I30" s="13" t="inlineStr">
         <is>
-          <t>ADELANTADA (era semana 9). Validacion de extremo a extremo sobre DLHM-model: holograma simulado con verdad-terreno conocida, retropropagado con MPASM. La fase reconstruida a la distancia nominal devuelve el target con los grupos de barras USAF y sus numeros legibles, sin ajustar parametros. Dos lecciones: el caso cae FUERA del rango de FFT-ASM (z_lim = 6.6 mm frente a z = 24 mm), y el criterio de autofoco depende del tipo de objeto (en fase hay que MINIMIZAR la varianza de amplitud, no maximizar nitidez). Falta versionarlo como scripts/reconstruccion_dlhm.py. Al 23/08 la maquinaria de retropropagacion ya esta versionada (tarea 64), asi que lo que queda es rehacer esa validacion llamando al paquete en vez del script suelto.</t>
+          <t>ADELANTADA (era semana 9). Validacion de extremo a extremo sobre DLHM-model: holograma simulado con verdad-terreno conocida, retropropagado con MPASM. La fase reconstruida a la distancia nominal devuelve el target con los grupos de barras USAF y sus numeros legibles, sin ajustar parametros. Dos lecciones: el caso cae FUERA del rango de FFT-ASM (z_lim = 6.6 mm frente a z = 24 mm), y el criterio de autofoco depende del tipo de objeto (en fase hay que MINIMIZAR la varianza de amplitud, no maximizar nitidez). Falta versionarlo como scripts/reconstruccion_dlhm.py. Al 23/08 la maquinaria de retropropagacion ya esta versionada (tarea 64), asi que lo que queda es rehacer esa validacion llamando al paquete en vez del script suelto. CERRADA el 27/09 con la tarea 78 (commit 17b6e2f510), fuera de su fecha del 18/09. La validacion ya llama al paquete (CamposT.dlhm) y queda versionada como scripts/verif_dlhm_esferico.py, no como scripts/reconstruccion_dlhm.py. Hologramas simulados con la ida exacta (3.6e-6 contra RS directo) de dos muestras sinteticas con verdad-terreno: un mosaico de detalle de ~1.25 um, reconstruido con corr 0.969 en la ventana entera del sensor de 3000 px (1.0000 hasta 3 grados), y el BenchmarkTarget de DLHM-model a z = 3 mm, del que un barrido por nitidez sobre el holograma de INTENSIDAD recupera z = 3.0005 mm sin conocer el objeto. La imagen gemela sigue sin suprimirse (corr 0.95 en el centro con intensidad, 1.000 con el campo complejo).</t>
         </is>
       </c>
     </row>
@@ -4615,7 +4615,7 @@
       </c>
       <c r="I81" s="13" t="inlineStr">
         <is>
-          <t>Commit 17b6e2f510. MPASM con la onda esferica EXACTA en los dos sentidos, sin aproximacion paraxial: CamposT/dlhm.py, con holograma() para simular y Reconstructor/reconstruir() para reconstruir; el Reconstructor calcula el espectro del sensor una sola vez para todo un barrido de z. La parte parabolica de e^{ikr}/r va DENTRO de las matrices de la DFT con integrales de Fresnel (ventana_chirp: la DFT exacta de una entrada de banda limitada por un chirp sin muestrear) y el residuo no paraxial punto a punto; la rejilla de frecuencias sale de la geometria, con banda mas ancha que 1/delta (Kf &lt; 1: expansion, no compresion), y se reconstruye c - 1 (con c, la referencia truncada en el borde del sensor bajaba la corr de 0.90 a 0.27). SUPERA LA RECOMENDACION (i) DE LA TAREA 24: el escalado z_eq en la malla delta/M solo se habia validado con objetos lisos de 6 a 30 um; con detalle de ~1.25 um su ida contra Rayleigh-Sommerfeld directo da error 0.47 en el eje, 0.65 a 5.7 grados y 0.89 a 12.4, y la exacta 3.6e-6 en los tres. Sensor entero (N = 3000, borde a 15.3 grados): corr con el objeto 0.969 en la ventana entera (1.0000 hasta 3 grados, 0.925 en la esquina) contra 0.683 del escalado; la misma rejilla sin las ventanas de Fresnel da 0.516, y en N = 2048 entre 0.42 y 0.946 segun el periodo P: acierta por geometria, no por construccion. Coste por z igual al escalado: 0.36 frente a 0.33 s en N = 3000; con 3000x4000 px son 5200x7712 frecuencias (306 MB en complex64), 9.8 s una vez y 0.56 s por z en la RTX 3050. Autofoco por nitidez sobre un holograma de INTENSIDAD del BenchmarkTarget a z = 3 mm: la exacta encuentra 3.0005 mm y el escalado se va al extremo del barrido. Contrastada con reconstruir() de mi_prueba_dlhm (la cadena de Carlos): corr 0.993 con malla PAR y remuestreo de banda limitada; con la malla impar que da malla_remuestreada (2027) solo 0.875, porque su linspace no pasa por f = 0 y desplaza ~1 um. tests/test_dlhm.py: 21 pruebas, 10 de 10 mutaciones detectadas; scripts/verif_dlhm_esferico.py reproduce las cifras; scipy pasa a dependencia. 486 passed, 4 skipped. Rama claude/dlhm-mpasm-esferico, sin fusionar al 27/09. DEUDAS ABIERTAS: la malla impar de malla_remuestreada sigue sin corregir; la imagen gemela no se suprime; no se modela la integracion del pixel; la ida del sensor entero tarda 34 s en GPU; falta decidir si esto cierra las tareas 25 y 27; y hay que revisar la diapositiva 9 (Kf) y el PDF de la tarea 24.</t>
+          <t>Commit 17b6e2f510. MPASM con la onda esferica EXACTA en los dos sentidos, sin aproximacion paraxial: CamposT/dlhm.py, con holograma() para simular y Reconstructor/reconstruir() para reconstruir; el Reconstructor calcula el espectro del sensor una sola vez para todo un barrido de z. La parte parabolica de e^{ikr}/r va DENTRO de las matrices de la DFT con integrales de Fresnel (ventana_chirp: la DFT exacta de una entrada de banda limitada por un chirp sin muestrear) y el residuo no paraxial punto a punto; la rejilla de frecuencias sale de la geometria, con banda mas ancha que 1/delta (Kf &lt; 1: expansion, no compresion), y se reconstruye c - 1 (con c, la referencia truncada en el borde del sensor bajaba la corr de 0.90 a 0.27). SUPERA LA RECOMENDACION (i) DE LA TAREA 24: el escalado z_eq en la malla delta/M solo se habia validado con objetos lisos de 6 a 30 um; con detalle de ~1.25 um su ida contra Rayleigh-Sommerfeld directo da error 0.47 en el eje, 0.65 a 5.7 grados y 0.89 a 12.4, y la exacta 3.6e-6 en los tres. Sensor entero (N = 3000, borde a 15.3 grados): corr con el objeto 0.969 en la ventana entera (1.0000 hasta 3 grados, 0.925 en la esquina) contra 0.683 del escalado; la misma rejilla sin las ventanas de Fresnel da 0.516, y en N = 2048 entre 0.42 y 0.946 segun el periodo P: acierta por geometria, no por construccion. Coste por z igual al escalado: 0.36 frente a 0.33 s en N = 3000; con 3000x4000 px son 5200x7712 frecuencias (306 MB en complex64), 9.8 s una vez y 0.56 s por z en la RTX 3050. Autofoco por nitidez sobre un holograma de INTENSIDAD del BenchmarkTarget a z = 3 mm: la exacta encuentra 3.0005 mm y el escalado se va al extremo del barrido. Contrastada con reconstruir() de mi_prueba_dlhm (la cadena de Carlos): corr 0.993 con malla PAR y remuestreo de banda limitada; con la malla impar que da malla_remuestreada (2027) solo 0.875, porque su linspace no pasa por f = 0 y desplaza ~1 um. tests/test_dlhm.py: 21 pruebas, 10 de 10 mutaciones detectadas; scripts/verif_dlhm_esferico.py reproduce las cifras; scipy pasa a dependencia. 486 passed, 4 skipped. Fusionada a main el 27/09. Cierra las tareas 25 y 27, decidido el 27/09. DEUDAS ABIERTAS: la malla impar de malla_remuestreada sigue sin corregir; la imagen gemela no se suprime; no se modela la integracion del pixel; la ida del sensor entero tarda 34 s en GPU; y hay que revisar la diapositiva 9 (Kf) y el PDF de la tarea 24.</t>
         </is>
       </c>
     </row>

--- a/docs/Cronograma_TG_DLHM.xlsx
+++ b/docs/Cronograma_TG_DLHM.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Hitos" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tareas'!$A$3:$I$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tareas'!$A$3:$I$82</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
@@ -1314,7 +1314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="7" customWidth="1" style="22" min="1" max="1"/>
@@ -4619,8 +4619,51 @@
         </is>
       </c>
     </row>
+    <row r="82" ht="25.5" customHeight="1" s="22">
+      <c r="A82" s="12" t="n">
+        <v>79</v>
+      </c>
+      <c r="B82" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C82" s="12" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="D82" s="13" t="inlineStr">
+        <is>
+          <t>Portar la seleccion de foco de barrido_foco a mi_prueba_dlhm (motores exacto y de Carlos) y anadir el modelo de Lopera como segundo simulador</t>
+        </is>
+      </c>
+      <c r="E82" s="13" t="inlineStr">
+        <is>
+          <t>scripts/mi_prueba_dlhm.py + tests/test_mi_prueba_dlhm_seleccion.py + arreglo de CamposT/dlhm.py</t>
+        </is>
+      </c>
+      <c r="F82" s="12" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="G82" s="12" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="H82" s="12" t="inlineStr">
+        <is>
+          <t>02/10/2026</t>
+        </is>
+      </c>
+      <c r="I82" s="13" t="inlineStr">
+        <is>
+          <t>Commits 4e08e49050 (CamposT/dlhm.py) y dfe6fe7a27. mi_prueba_dlhm.py elige el foco con los parametros de seleccion de barrido_foco (Tamura, Pearson y SSIM sobre la misma reconstruccion, grueso + fino, ROI o cuarto central, tabla, curvas.npz y dos figuras; metricas copiadas con prueba ast) y dos motores: exacto (CamposT.dlhm, holograma entero) y de Carlos (reconstruir() sobre el recorte: hay que dividir por |U0|^2 -0.84 frente a 0.21-, tomar la huella del 1/M central y usar un ROI cuadrado). BenchmarkTarget simulado 3000x4000 a z = 3 mm: exacto 3.0000 en las tres metricas, tambien con Z_REAL a medio paso de la rejilla; Carlos (ROI 1024) a 2 um; objeto de fase, -Tamura a 1 um. El ~0.03 del script viejo era la geometria de referencia_a_escala(): +0.051 frente a -0.731 con la huella. Arreglado de paso holograma() de CamposT/dlhm.py: el soporte recortaba la frecuencia del otro eje a 1/lambda y pedia 86.7 GB con 3000x4000; ahora 40 s en GPU y RS sigue en 3.7e-6. SIMULADOR = 'lopera': el modelo de Lopera et al. 2024 (su dlhm() copiada literal, verificada bit a bit contra su codigo): su holograma reconstruido exacto enfoca +14 a +20 um fuera de Z_REAL; sin Brown-Conrady, envolvente ni 8 bits sigue (+16 a +27 um): es su nucleo paraxial (contra la ida exacta, 1.00000 con objeto liso y 0.895 con detalle fino). 49 pruebas nuevas; suite 551 passed.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:I81"/>
+  <autoFilter ref="A3:I82"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
